--- a/DateBase/orders/Nha Thu_2026-8-3.xlsx
+++ b/DateBase/orders/Nha Thu_2026-8-3.xlsx
@@ -867,6 +867,9 @@
       <c r="C51" t="str">
         <v>597_尤加利叶小叶_undefined_undefined_1bunch</v>
       </c>
+      <c r="F51" t="str">
+        <v>15</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
@@ -925,7 +928,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>0101010105101015105510101515515712107101051010510555651515301010101030102055555150</v>
+        <v>01010101051010151055101015155157121071010510105105556515153010101010301020555551515</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Nha Thu_2026-8-3.xlsx
+++ b/DateBase/orders/Nha Thu_2026-8-3.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L51"/>
+  <dimension ref="A1:L67"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -871,9 +871,156 @@
         <v>15</v>
       </c>
     </row>
+    <row r="52" xml:space="preserve">
+      <c r="A52" t="str">
+        <v>1</v>
+      </c>
+      <c r="C52" t="str" xml:space="preserve">
+        <v xml:space="preserve">373_龙柳_Salix
+_undefined_1bunch</v>
+      </c>
+      <c r="F52" t="str">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="str">
+        <v>4</v>
+      </c>
+      <c r="C53" t="str">
+        <v>184_微光_shimmer_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F53" t="str">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="str">
+        <v/>
+      </c>
+      <c r="C54" t="str">
+        <v>165_杏仁酒_Amaretto_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F54" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="C55" t="str">
+        <v>149_骄傲_Proud_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F55" t="str">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="C56" t="str">
+        <v>148_坦尼克_Tineke_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F56" t="str">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="C57" t="str">
+        <v>225_果汁阳台_Juicy Terrazza_Rosa rugosa Thunb._10stems</v>
+      </c>
+      <c r="F57" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="C58" t="str">
+        <v>436_木百合_leucadendron _undefined_1bunch</v>
+      </c>
+      <c r="F58" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="str">
+        <v>5</v>
+      </c>
+      <c r="C59" t="str">
+        <v>209_海洋之歌_Ocean Song_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F59" t="str">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="C60" t="str">
+        <v>188_戴安娜_Diana_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F60" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="C61" t="str">
+        <v>203_佛罗伊德_Floyd_Rosa rugosa Thunb._20stems</v>
+      </c>
+      <c r="F61" t="str">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="C62" t="str">
+        <v>522_山归来绿_Smilax china_undefined_1bunch</v>
+      </c>
+      <c r="F62" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="C63" t="str">
+        <v>277_草莓杏仁饼_undefined_Rosa rugosa Thunb._10stems</v>
+      </c>
+      <c r="F63" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="str">
+        <v>6</v>
+      </c>
+      <c r="C64" t="str">
+        <v>640_红辣椒_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F64" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="C65" t="str">
+        <v>640_红辣椒_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F65" t="str">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="C66" t="str">
+        <v>453_国产菠萝_undefined_undefined_1bunch</v>
+      </c>
+      <c r="F66" t="str">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="str">
+        <v>7</v>
+      </c>
+      <c r="C67" t="str">
+        <v>504_大花葱 直_Allium _undefined_1bunch</v>
+      </c>
+      <c r="F67" t="str">
+        <v>40</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L51"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L67"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -928,7 +1075,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>01010101051010151055101015155157121071010510105105556515153010101010301020555551515</v>
+        <v>010101010510101510551010151551571210710105101051055565151530101010103010205555515152041011155541011510510540</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Nha Thu_2026-8-3.xlsx
+++ b/DateBase/orders/Nha Thu_2026-8-3.xlsx
@@ -1077,6 +1077,9 @@
       <c r="G2" t="str">
         <v>010101010510101510551010151551571210710105101051055565151530101010103010205555515152041011155541011510510540</v>
       </c>
+      <c r="H2" t="str">
+        <v>CNY</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
